--- a/src/assets/csv_templates/BBBP-Water-Data-Collection-Form-modified.xlsx
+++ b/src/assets/csv_templates/BBBP-Water-Data-Collection-Form-modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ak1\Dropbox (ORNL)\Better Plants\Annual Reporting Forms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/txr/dev/VERIFI/src/assets/csv_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED7355-D58B-435E-8A77-B5F027C43E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88112727-4E57-7F4E-9209-9D3025F93795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="19420" windowHeight="19820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1149,26 +1149,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1182,19 +1179,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1214,29 +1211,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1247,52 +1241,50 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1306,33 +1298,30 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1342,47 +1331,44 @@
     <xf numFmtId="3" fontId="3" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,84 +1386,79 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1485,67 +1466,23 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1561,49 +1498,86 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="15" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1893,8 +1867,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2085341" y="849119"/>
-          <a:ext cx="10481154" cy="215899"/>
+          <a:off x="2085341" y="864607"/>
+          <a:ext cx="11580788" cy="215899"/>
           <a:chOff x="4170" y="943"/>
           <a:chExt cx="11400" cy="2"/>
         </a:xfrm>
@@ -2352,8 +2326,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="17641074"/>
-          <a:ext cx="12626123" cy="161925"/>
+          <a:off x="0" y="17648818"/>
+          <a:ext cx="13741245" cy="161925"/>
           <a:chOff x="4170" y="943"/>
           <a:chExt cx="11400" cy="2"/>
         </a:xfrm>
@@ -3174,8 +3148,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3447705" y="948843"/>
-          <a:ext cx="10664689" cy="283635"/>
+          <a:off x="3694008" y="963082"/>
+          <a:ext cx="11698392" cy="283635"/>
           <a:chOff x="4170" y="943"/>
           <a:chExt cx="11400" cy="2"/>
         </a:xfrm>
@@ -3607,496 +3581,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>86591</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>21166</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>259774</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="9" name="Group 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr>
-          <a:grpSpLocks/>
-        </xdr:cNvGrpSpPr>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1327727" y="27728333"/>
-          <a:ext cx="12865484" cy="173183"/>
-          <a:chOff x="4170" y="944"/>
-          <a:chExt cx="11400" cy="2"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Freeform 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr>
-            <a:spLocks/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="4170" y="944"/>
-            <a:ext cx="11400" cy="2"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst>
-              <a:gd name="T0" fmla="+- 0 4118 4118"/>
-              <a:gd name="T1" fmla="*/ T0 w 7402"/>
-              <a:gd name="T2" fmla="+- 0 11520 4118"/>
-              <a:gd name="T3" fmla="*/ T2 w 7402"/>
-            </a:gdLst>
-            <a:ahLst/>
-            <a:cxnLst>
-              <a:cxn ang="0">
-                <a:pos x="T1" y="0"/>
-              </a:cxn>
-              <a:cxn ang="0">
-                <a:pos x="T3" y="0"/>
-              </a:cxn>
-            </a:cxnLst>
-            <a:rect l="0" t="0" r="r" b="b"/>
-            <a:pathLst>
-              <a:path w="7402">
-                <a:moveTo>
-                  <a:pt x="0" y="0"/>
-                </a:moveTo>
-                <a:lnTo>
-                  <a:pt x="7402" y="0"/>
-                </a:lnTo>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:noFill/>
-          <a:ln w="50800">
-            <a:solidFill>
-              <a:srgbClr val="1D428A"/>
-            </a:solidFill>
-            <a:round/>
-            <a:headEnd/>
-            <a:tailEnd/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="t" anchorCtr="0" upright="1">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle>
-            <a:defPPr>
-              <a:defRPr lang="en-US"/>
-            </a:defPPr>
-            <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl1pPr>
-            <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl2pPr>
-            <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl3pPr>
-            <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl4pPr>
-            <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl5pPr>
-            <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl6pPr>
-            <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl7pPr>
-            <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl8pPr>
-            <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-              <a:defRPr sz="1800" kern="1200">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:lvl9pPr>
-          </a:lstStyle>
-          <a:p>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>923293</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>147555</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1696</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>33948</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="12685225" y="25071305"/>
-          <a:ext cx="824653" cy="261620"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>822614</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>95393</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>527782</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>11631</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Text Box 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1226705" y="25019143"/>
-          <a:ext cx="6574713" cy="291465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="0" bIns="45720" anchor="ctr" anchorCtr="0">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="en-US"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="12700" marR="0">
-            <a:lnSpc>
-              <a:spcPts val="1195"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Learn</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" spc="60">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" spc="-5">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>more</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" spc="60">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>at</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" spc="65">
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" spc="-5">
-              <a:solidFill>
-                <a:srgbClr val="007A3E"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>energy.gov/eere/amo/better-plants</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:effectLst/>
-            <a:latin typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Lucida Sans" panose="020B0602030504020204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>654243</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -4202,6 +3686,56 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>750453</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>2232121</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>481060</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>90921</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2203D57-1D73-4852-0881-7E009E985B55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1212271" y="27574394"/>
+          <a:ext cx="14720456" cy="956830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4495,628 +4029,616 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="57" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" style="3" customWidth="1"/>
-    <col min="3" max="8" width="9.1796875" style="3"/>
-    <col min="9" max="9" width="16" style="3" customWidth="1"/>
-    <col min="10" max="13" width="9.1796875" style="3"/>
-    <col min="14" max="14" width="2.1796875" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9.1796875" style="3"/>
+    <col min="1" max="1" width="57" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="8" width="9.1640625" style="1"/>
+    <col min="9" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="13" width="9.1640625" style="1"/>
+    <col min="14" max="14" width="2.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K1" s="27"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K2" s="27"/>
-    </row>
-    <row r="3" spans="1:14" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106"/>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-    </row>
-    <row r="4" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="100"/>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-    </row>
-    <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="K2" s="23"/>
+    </row>
+    <row r="3" spans="1:14" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="149"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
+      <c r="K3" s="149"/>
+      <c r="L3" s="149"/>
+      <c r="M3" s="149"/>
+      <c r="N3" s="149"/>
+    </row>
+    <row r="4" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="88"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+    </row>
+    <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-    </row>
-    <row r="6" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="105"/>
-    </row>
-    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="134"/>
+      <c r="N6" s="135"/>
+    </row>
+    <row r="7" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="105"/>
-    </row>
-    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="134"/>
+      <c r="N7" s="135"/>
+    </row>
+    <row r="8" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="105"/>
-    </row>
-    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="134"/>
+      <c r="K8" s="134"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
+      <c r="N8" s="135"/>
+    </row>
+    <row r="9" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="105"/>
-    </row>
-    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="134"/>
+      <c r="N9" s="135"/>
+    </row>
+    <row r="10" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="105"/>
-    </row>
-    <row r="11" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="134"/>
+      <c r="N10" s="135"/>
+    </row>
+    <row r="11" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="104"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="105"/>
-    </row>
-    <row r="12" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="135"/>
+    </row>
+    <row r="12" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="105"/>
-    </row>
-    <row r="13" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="C12" s="134"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="134"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="134"/>
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="134"/>
+      <c r="N12" s="135"/>
+    </row>
+    <row r="13" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="105"/>
-    </row>
-    <row r="14" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="135"/>
+    </row>
+    <row r="14" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="105"/>
-    </row>
-    <row r="15" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="78" t="s">
+      <c r="C14" s="134"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="135"/>
+    </row>
+    <row r="15" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="113"/>
-    </row>
-    <row r="16" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="78" t="s">
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="141"/>
+      <c r="N15" s="153"/>
+    </row>
+    <row r="16" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="133" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="105"/>
-    </row>
-    <row r="17" spans="1:14" ht="227.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="C16" s="134"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="134"/>
+      <c r="N16" s="135"/>
+    </row>
+    <row r="17" spans="1:14" ht="227.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="112" t="s">
+      <c r="B17" s="136" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="104"/>
-      <c r="N17" s="105"/>
-    </row>
-    <row r="18" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="135"/>
+    </row>
+    <row r="18" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="105"/>
-    </row>
-    <row r="19" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="78" t="s">
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="135"/>
+    </row>
+    <row r="19" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="151" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="109"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="109"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="110"/>
-    </row>
-    <row r="20" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="152"/>
+    </row>
+    <row r="20" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="105"/>
-    </row>
-    <row r="21" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="78" t="s">
+      <c r="C20" s="134"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="135"/>
+    </row>
+    <row r="21" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="103" t="s">
+      <c r="B21" s="133" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="29"/>
-    </row>
-    <row r="22" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78" t="s">
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="141"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="25"/>
+    </row>
+    <row r="22" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="118"/>
-    </row>
-    <row r="23" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78" t="s">
+      <c r="C22" s="141"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="141"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="141"/>
+      <c r="L22" s="141"/>
+      <c r="M22" s="141"/>
+      <c r="N22" s="142"/>
+    </row>
+    <row r="23" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="123" t="s">
+      <c r="B23" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="125"/>
-    </row>
-    <row r="24" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="146"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="147"/>
+    </row>
+    <row r="24" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="103" t="s">
+      <c r="B24" s="133" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="105"/>
-    </row>
-    <row r="25" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="78" t="s">
+      <c r="C24" s="134"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="135"/>
+    </row>
+    <row r="25" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="133" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="118"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="116" t="s">
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
+    </row>
+    <row r="26" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="139" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="107"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="107"/>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="117"/>
-      <c r="B27" s="107"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="107"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
+      <c r="C26" s="150"/>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="150"/>
+      <c r="H26" s="150"/>
+      <c r="I26" s="150"/>
+      <c r="J26" s="150"/>
+      <c r="K26" s="150"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="150"/>
+      <c r="N26" s="150"/>
+    </row>
+    <row r="27" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="140"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
+      <c r="K27" s="150"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="150"/>
+      <c r="N27" s="150"/>
+    </row>
+    <row r="28" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="121" t="s">
+      <c r="B28" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="121"/>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="121"/>
-      <c r="G28" s="121"/>
-      <c r="H28" s="121"/>
-      <c r="I28" s="121"/>
-      <c r="J28" s="121"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="121"/>
-      <c r="N28" s="122"/>
-    </row>
-    <row r="29" spans="1:14" s="101" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="126"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="126"/>
-      <c r="E29" s="126"/>
-      <c r="F29" s="126"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="126"/>
-      <c r="I29" s="126"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="126"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-    </row>
-    <row r="30" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="119"/>
-      <c r="B30" s="120"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="120"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="120"/>
-      <c r="M30" s="120"/>
-      <c r="N30" s="120"/>
-    </row>
-    <row r="31" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="114"/>
-      <c r="B31" s="115"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="115"/>
-      <c r="N31" s="115"/>
-    </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="114"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
-      <c r="H32" s="115"/>
-      <c r="I32" s="115"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="115"/>
-      <c r="N32" s="115"/>
-    </row>
-    <row r="33" spans="1:14" s="9" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
+      <c r="C28" s="134"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="134"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="134"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="134"/>
+      <c r="N28" s="135"/>
+    </row>
+    <row r="29" spans="1:14" s="89" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="148"/>
+      <c r="B29" s="148"/>
+      <c r="C29" s="148"/>
+      <c r="D29" s="148"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
+      <c r="G29" s="148"/>
+      <c r="H29" s="148"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="148"/>
+      <c r="K29" s="148"/>
+      <c r="L29" s="148"/>
+      <c r="M29" s="148"/>
+      <c r="N29" s="148"/>
+    </row>
+    <row r="30" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="143"/>
+      <c r="B30" s="144"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="144"/>
+      <c r="I30" s="144"/>
+      <c r="J30" s="144"/>
+      <c r="K30" s="144"/>
+      <c r="L30" s="144"/>
+      <c r="M30" s="144"/>
+      <c r="N30" s="144"/>
+    </row>
+    <row r="31" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="137"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="138"/>
+    </row>
+    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="137"/>
+      <c r="B32" s="138"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
+      <c r="M32" s="138"/>
+      <c r="N32" s="138"/>
+    </row>
+    <row r="33" spans="1:14" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="23" t="s">
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="23" t="s">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.15">
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="20" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B12:N12"/>
-    <mergeCell ref="B18:N18"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B22:N22"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B23:N23"/>
-    <mergeCell ref="B25:N25"/>
-    <mergeCell ref="B20:N20"/>
-    <mergeCell ref="A29:N29"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B16:N16"/>
     <mergeCell ref="A3:N3"/>
@@ -5133,6 +4655,18 @@
     <mergeCell ref="B15:N15"/>
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B12:N12"/>
+    <mergeCell ref="B18:N18"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B23:N23"/>
+    <mergeCell ref="B25:N25"/>
+    <mergeCell ref="B20:N20"/>
+    <mergeCell ref="A29:N29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5147,1193 +4681,1169 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:P95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.1796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.453125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="41.81640625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="30.7265625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="24" style="3" customWidth="1"/>
-    <col min="15" max="15" width="38.453125" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9.1796875" style="3"/>
+    <col min="10" max="10" width="8.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="41.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.5" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:12" x14ac:dyDescent="0.15">
       <c r="D1" s="2"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="I1" s="19"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="3:12" x14ac:dyDescent="0.15">
       <c r="D2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="23"/>
-    </row>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="3:12" x14ac:dyDescent="0.15">
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="3:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="3:12" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="3:12" ht="13" x14ac:dyDescent="0.3">
-      <c r="C7" s="35"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="3:12" ht="13" x14ac:dyDescent="0.3">
-      <c r="C8" s="35"/>
-      <c r="D8" s="15" t="s">
+    <row r="4" spans="3:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="3:12" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="51"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C7" s="31"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C8" s="31"/>
+      <c r="D8" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="169"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="36"/>
-      <c r="D9" s="16" t="s">
+      <c r="E8" s="119"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C9" s="32"/>
+      <c r="D9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="169"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="36"/>
-      <c r="D10" s="16" t="s">
+      <c r="E9" s="119"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="32"/>
+      <c r="D10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="159"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="161"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="35"/>
-      <c r="D11" s="16" t="s">
+      <c r="E10" s="97"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C11" s="31"/>
+      <c r="D11" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="169"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="35"/>
-      <c r="D12" s="16" t="s">
+      <c r="E11" s="119"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="3:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C12" s="31"/>
+      <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="169"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="3:12" ht="13" x14ac:dyDescent="0.3">
-      <c r="C13" s="35"/>
-      <c r="D13" s="16" t="s">
+      <c r="E12" s="119"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C13" s="31"/>
+      <c r="D13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="148"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="3:12" ht="13" x14ac:dyDescent="0.3">
-      <c r="C14" s="35"/>
-      <c r="D14" s="16" t="s">
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C14" s="31"/>
+      <c r="D14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="3:12" ht="13" x14ac:dyDescent="0.3">
-      <c r="C15" s="35"/>
-      <c r="D15" s="15" t="s">
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="3:12" x14ac:dyDescent="0.15">
+      <c r="C15" s="31"/>
+      <c r="D15" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
-      <c r="G15" s="164"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="3:12" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="38"/>
-      <c r="D16" s="15" t="s">
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C16" s="31"/>
+      <c r="D16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="162"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="164"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="3:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="38"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="3:15" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="38"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="17" t="s">
+      <c r="E16" s="100"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C17" s="31"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="31"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="3:15" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="38"/>
-      <c r="D19" s="45" t="s">
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="3:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C19" s="31"/>
+      <c r="D19" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="3:15" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="38"/>
-      <c r="D20" s="45" t="s">
+      <c r="E19" s="7"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="33"/>
+    </row>
+    <row r="20" spans="3:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C20" s="31"/>
+      <c r="D20" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="3:15" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="38"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="3:15" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="38"/>
-      <c r="D22" s="15" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="33"/>
+    </row>
+    <row r="21" spans="3:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C21" s="31"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="33"/>
+    </row>
+    <row r="22" spans="3:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C22" s="31"/>
+      <c r="D22" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-    </row>
-    <row r="23" spans="3:15" s="9" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="38"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="51" t="s">
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="33"/>
+    </row>
+    <row r="23" spans="3:15" ht="36.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" s="31"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="87"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="53"/>
-    </row>
-    <row r="24" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="48"/>
-      <c r="D24" s="54" t="s">
+      <c r="J23" s="33"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="47"/>
+    </row>
+    <row r="24" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="42"/>
+      <c r="D24" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="62" t="s">
+      <c r="E24" s="30"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J24" s="87"/>
-      <c r="K24" s="134"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="50"/>
-    </row>
-    <row r="25" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="48"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="62" t="s">
+      <c r="J24" s="33"/>
+      <c r="K24" s="132"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="44"/>
+    </row>
+    <row r="25" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="42"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="87"/>
-      <c r="K25" s="134"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="50"/>
-    </row>
-    <row r="26" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="38"/>
-      <c r="D26" s="54" t="s">
+      <c r="J25" s="33"/>
+      <c r="K25" s="132"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="44"/>
+    </row>
+    <row r="26" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C26" s="31"/>
+      <c r="D26" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="62" t="s">
+      <c r="E26" s="30"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="87"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="50"/>
-    </row>
-    <row r="27" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="38"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="62" t="s">
+      <c r="J26" s="33"/>
+      <c r="K26" s="132"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="44"/>
+    </row>
+    <row r="27" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C27" s="31"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="87"/>
-      <c r="K27" s="134"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="50"/>
-    </row>
-    <row r="28" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="38"/>
-      <c r="D28" s="54" t="s">
+      <c r="J27" s="33"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="44"/>
+    </row>
+    <row r="28" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C28" s="31"/>
+      <c r="D28" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="62" t="s">
+      <c r="E28" s="30"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J28" s="87"/>
-      <c r="K28" s="134"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="50"/>
-    </row>
-    <row r="29" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="38"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="62" t="s">
+      <c r="J28" s="33"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="44"/>
+    </row>
+    <row r="29" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C29" s="31"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J29" s="87"/>
-      <c r="K29" s="134"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="102"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="50"/>
-    </row>
-    <row r="30" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="38"/>
-      <c r="D30" s="54" t="s">
+      <c r="J29" s="33"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="44"/>
+    </row>
+    <row r="30" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C30" s="31"/>
+      <c r="D30" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="62" t="s">
+      <c r="E30" s="30"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J30" s="87"/>
-      <c r="K30" s="134"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="50"/>
-    </row>
-    <row r="31" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="38"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="62" t="s">
+      <c r="J30" s="33"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="44"/>
+    </row>
+    <row r="31" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C31" s="31"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="87"/>
-      <c r="K31" s="134"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="50"/>
-    </row>
-    <row r="32" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="38"/>
-      <c r="D32" s="54" t="s">
+      <c r="J31" s="33"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="44"/>
+    </row>
+    <row r="32" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C32" s="31"/>
+      <c r="D32" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="62" t="s">
+      <c r="E32" s="30"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J32" s="87"/>
-      <c r="K32" s="134"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="50"/>
-    </row>
-    <row r="33" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="38"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="62" t="s">
+      <c r="J32" s="33"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="44"/>
+    </row>
+    <row r="33" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C33" s="31"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="87"/>
-      <c r="K33" s="134"/>
-      <c r="L33" s="102"/>
-      <c r="M33" s="102"/>
-      <c r="N33" s="102"/>
-      <c r="O33" s="50"/>
-    </row>
-    <row r="34" spans="3:15" s="11" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="46"/>
-      <c r="D34" s="54" t="s">
+      <c r="J33" s="33"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="44"/>
+    </row>
+    <row r="34" spans="3:15" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C34" s="40"/>
+      <c r="D34" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="62" t="s">
+      <c r="E34" s="30"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="134"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="49"/>
-    </row>
-    <row r="35" spans="3:15" s="11" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="46"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="62" t="s">
+      <c r="J34" s="79"/>
+      <c r="K34" s="132"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+    </row>
+    <row r="35" spans="3:15" s="8" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C35" s="40"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="90"/>
-      <c r="K35" s="134"/>
-      <c r="L35" s="102"/>
-      <c r="M35" s="102"/>
-      <c r="N35" s="102"/>
-      <c r="O35" s="102"/>
-    </row>
-    <row r="36" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="38"/>
-      <c r="D36" s="54" t="s">
+      <c r="J35" s="79"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+    </row>
+    <row r="36" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C36" s="31"/>
+      <c r="D36" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="62" t="s">
+      <c r="E36" s="30"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="J36" s="87"/>
-      <c r="K36" s="134"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="50"/>
-    </row>
-    <row r="37" spans="3:15" s="9" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="38"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="62" t="s">
+      <c r="J36" s="33"/>
+      <c r="K36" s="132"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="44"/>
+    </row>
+    <row r="37" spans="3:15" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C37" s="31"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="J37" s="87"/>
-      <c r="K37" s="134"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="102"/>
-      <c r="N37" s="102"/>
-      <c r="O37" s="50"/>
-    </row>
-    <row r="38" spans="3:15" s="9" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="38"/>
-      <c r="D38" s="54" t="s">
+      <c r="J37" s="33"/>
+      <c r="K37" s="132"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="44"/>
+    </row>
+    <row r="38" spans="3:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C38" s="31"/>
+      <c r="D38" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="68"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="134"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="50"/>
-    </row>
-    <row r="39" spans="3:15" s="9" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="38"/>
-      <c r="D39" s="67" t="s">
+      <c r="E38" s="62"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="132"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="44"/>
+    </row>
+    <row r="39" spans="3:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C39" s="31"/>
+      <c r="D39" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="74"/>
-      <c r="J39" s="87"/>
-      <c r="K39" s="134"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="50"/>
-    </row>
-    <row r="40" spans="3:15" s="9" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="38"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="87"/>
-      <c r="K40" s="134"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="50"/>
-    </row>
-    <row r="41" spans="3:15" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="38"/>
-      <c r="D41" s="45" t="s">
+      <c r="E39" s="62"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="44"/>
+    </row>
+    <row r="40" spans="3:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C40" s="31"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="44"/>
+    </row>
+    <row r="41" spans="3:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C41" s="31"/>
+      <c r="D41" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="75"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="134"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="49"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="50"/>
-    </row>
-    <row r="42" spans="3:15" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="38"/>
-      <c r="D42" s="45" t="s">
+      <c r="E41" s="66"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="132"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+      <c r="N41" s="43"/>
+      <c r="O41" s="44"/>
+    </row>
+    <row r="42" spans="3:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C42" s="31"/>
+      <c r="D42" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="165"/>
-      <c r="F42" s="166"/>
-      <c r="G42" s="166"/>
-      <c r="H42" s="166"/>
-      <c r="I42" s="167"/>
-      <c r="J42" s="87"/>
-      <c r="K42" s="134"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="50"/>
-    </row>
-    <row r="43" spans="3:15" s="9" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="38"/>
-      <c r="D43" s="45" t="s">
+      <c r="E42" s="103"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="43"/>
+      <c r="O42" s="44"/>
+    </row>
+    <row r="43" spans="3:15" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C43" s="31"/>
+      <c r="D43" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="76"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="50"/>
-    </row>
-    <row r="44" spans="3:15" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="38"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="87"/>
-    </row>
-    <row r="45" spans="3:15" s="9" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="38"/>
-      <c r="D45" s="15" t="s">
+      <c r="E43" s="67"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="132"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="43"/>
+      <c r="O43" s="44"/>
+    </row>
+    <row r="44" spans="3:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="31"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="33"/>
+    </row>
+    <row r="45" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C45" s="31"/>
+      <c r="D45" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E45" s="77"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="92"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="87"/>
-    </row>
-    <row r="46" spans="3:15" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="38"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="93"/>
-      <c r="F46" s="93"/>
-      <c r="G46" s="93"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="87"/>
-    </row>
-    <row r="47" spans="3:15" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="38"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="41" t="s">
+      <c r="E45" s="68"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="33"/>
+    </row>
+    <row r="46" spans="3:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C46" s="31"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="33"/>
+    </row>
+    <row r="47" spans="3:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="31"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F47" s="51" t="s">
+      <c r="F47" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="93"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="56"/>
-    </row>
-    <row r="48" spans="3:15" s="9" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="38"/>
-      <c r="D48" s="55" t="s">
+      <c r="G47" s="81"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="50"/>
+    </row>
+    <row r="48" spans="3:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C48" s="31"/>
+      <c r="D48" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="93"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="87"/>
-    </row>
-    <row r="49" spans="3:12" s="9" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="38"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="87"/>
-    </row>
-    <row r="50" spans="3:12" s="9" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="38"/>
-      <c r="D50" s="55" t="s">
+      <c r="E48" s="24"/>
+      <c r="F48" s="60"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="33"/>
+    </row>
+    <row r="49" spans="3:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="31"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="33"/>
+    </row>
+    <row r="50" spans="3:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C50" s="31"/>
+      <c r="D50" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="94"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="87"/>
-    </row>
-    <row r="51" spans="3:12" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="38"/>
-      <c r="D51" s="15" t="s">
+      <c r="E50" s="82"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="33"/>
+    </row>
+    <row r="51" spans="3:10" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C51" s="31"/>
+      <c r="D51" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="94"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="87"/>
-    </row>
-    <row r="52" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="38"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="42"/>
-      <c r="J52" s="87"/>
-    </row>
-    <row r="53" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="38"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="87"/>
-    </row>
-    <row r="54" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="38"/>
-      <c r="D54" s="135" t="s">
+      <c r="E51" s="82"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="33"/>
+    </row>
+    <row r="52" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C52" s="31"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="33"/>
+    </row>
+    <row r="53" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C53" s="31"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="33"/>
+    </row>
+    <row r="54" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C54" s="31"/>
+      <c r="D54" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="E54" s="136"/>
-      <c r="F54" s="136"/>
-      <c r="G54" s="136"/>
-      <c r="H54" s="136"/>
-      <c r="I54" s="137"/>
-      <c r="J54" s="87"/>
-    </row>
-    <row r="55" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="38"/>
-      <c r="D55" s="138"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="139"/>
-      <c r="I55" s="140"/>
-      <c r="J55" s="87"/>
-    </row>
-    <row r="56" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="38"/>
-      <c r="D56" s="141"/>
-      <c r="E56" s="142"/>
-      <c r="F56" s="142"/>
-      <c r="G56" s="142"/>
-      <c r="H56" s="142"/>
-      <c r="I56" s="143"/>
-      <c r="J56" s="87"/>
-    </row>
-    <row r="57" spans="3:12" s="9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="38"/>
-      <c r="D57" s="141"/>
-      <c r="E57" s="142"/>
-      <c r="F57" s="142"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="143"/>
-      <c r="J57" s="87"/>
-    </row>
-    <row r="58" spans="3:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="38"/>
-      <c r="D58" s="144"/>
-      <c r="E58" s="145"/>
-      <c r="F58" s="145"/>
-      <c r="G58" s="145"/>
-      <c r="H58" s="145"/>
-      <c r="I58" s="145"/>
-      <c r="J58" s="87"/>
-    </row>
-    <row r="59" spans="3:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="38"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="87"/>
-    </row>
-    <row r="60" spans="3:12" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="38"/>
-      <c r="D60" s="135" t="s">
+      <c r="E54" s="95"/>
+      <c r="F54" s="95"/>
+      <c r="G54" s="95"/>
+      <c r="H54" s="95"/>
+      <c r="I54" s="96"/>
+      <c r="J54" s="33"/>
+    </row>
+    <row r="55" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C55" s="31"/>
+      <c r="D55" s="106"/>
+      <c r="E55" s="107"/>
+      <c r="F55" s="107"/>
+      <c r="G55" s="107"/>
+      <c r="H55" s="107"/>
+      <c r="I55" s="108"/>
+      <c r="J55" s="33"/>
+    </row>
+    <row r="56" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C56" s="31"/>
+      <c r="D56" s="109"/>
+      <c r="E56" s="110"/>
+      <c r="F56" s="110"/>
+      <c r="G56" s="110"/>
+      <c r="H56" s="110"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="33"/>
+    </row>
+    <row r="57" spans="3:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C57" s="31"/>
+      <c r="D57" s="109"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="110"/>
+      <c r="G57" s="110"/>
+      <c r="H57" s="110"/>
+      <c r="I57" s="111"/>
+      <c r="J57" s="33"/>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C58" s="31"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="113"/>
+      <c r="G58" s="113"/>
+      <c r="H58" s="113"/>
+      <c r="I58" s="113"/>
+      <c r="J58" s="33"/>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C59" s="31"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="33"/>
+    </row>
+    <row r="60" spans="3:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C60" s="31"/>
+      <c r="D60" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="136"/>
-      <c r="F60" s="136"/>
-      <c r="G60" s="136"/>
-      <c r="H60" s="136"/>
-      <c r="I60" s="137"/>
-      <c r="J60" s="87"/>
-    </row>
-    <row r="61" spans="3:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="38"/>
-      <c r="D61" s="138"/>
-      <c r="E61" s="139"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="139"/>
-      <c r="H61" s="139"/>
-      <c r="I61" s="140"/>
-      <c r="J61" s="87"/>
-    </row>
-    <row r="62" spans="3:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="38"/>
-      <c r="D62" s="141"/>
-      <c r="E62" s="142"/>
-      <c r="F62" s="142"/>
-      <c r="G62" s="142"/>
-      <c r="H62" s="142"/>
-      <c r="I62" s="143"/>
-      <c r="J62" s="87"/>
-    </row>
-    <row r="63" spans="3:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="38"/>
-      <c r="D63" s="141"/>
-      <c r="E63" s="142"/>
-      <c r="F63" s="142"/>
-      <c r="G63" s="142"/>
-      <c r="H63" s="142"/>
-      <c r="I63" s="143"/>
-      <c r="J63" s="87"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-    </row>
-    <row r="64" spans="3:12" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="38"/>
-      <c r="D64" s="144"/>
-      <c r="E64" s="145"/>
-      <c r="F64" s="145"/>
-      <c r="G64" s="145"/>
-      <c r="H64" s="145"/>
-      <c r="I64" s="145"/>
-      <c r="J64" s="87"/>
-    </row>
-    <row r="65" spans="3:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="35"/>
-      <c r="D65" s="95"/>
-      <c r="E65" s="95"/>
-      <c r="F65" s="95"/>
-      <c r="G65" s="95"/>
-      <c r="H65" s="95"/>
-      <c r="I65" s="95"/>
-      <c r="J65" s="37"/>
-    </row>
-    <row r="66" spans="3:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="35"/>
-      <c r="D66" s="95"/>
-      <c r="E66" s="95"/>
-      <c r="F66" s="95"/>
-      <c r="G66" s="95"/>
-      <c r="H66" s="95"/>
-      <c r="I66" s="95"/>
-      <c r="J66" s="37"/>
-    </row>
-    <row r="67" spans="3:10" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="35"/>
-      <c r="D67" s="149" t="s">
+      <c r="E60" s="95"/>
+      <c r="F60" s="95"/>
+      <c r="G60" s="95"/>
+      <c r="H60" s="95"/>
+      <c r="I60" s="96"/>
+      <c r="J60" s="33"/>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C61" s="31"/>
+      <c r="D61" s="106"/>
+      <c r="E61" s="107"/>
+      <c r="F61" s="107"/>
+      <c r="G61" s="107"/>
+      <c r="H61" s="107"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="33"/>
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C62" s="31"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110"/>
+      <c r="I62" s="111"/>
+      <c r="J62" s="33"/>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C63" s="31"/>
+      <c r="D63" s="109"/>
+      <c r="E63" s="110"/>
+      <c r="F63" s="110"/>
+      <c r="G63" s="110"/>
+      <c r="H63" s="110"/>
+      <c r="I63" s="111"/>
+      <c r="J63" s="33"/>
+    </row>
+    <row r="64" spans="3:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="31"/>
+      <c r="D64" s="112"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="113"/>
+      <c r="G64" s="113"/>
+      <c r="H64" s="113"/>
+      <c r="I64" s="113"/>
+      <c r="J64" s="33"/>
+    </row>
+    <row r="65" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C65" s="31"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="83"/>
+      <c r="G65" s="83"/>
+      <c r="H65" s="83"/>
+      <c r="I65" s="83"/>
+      <c r="J65" s="33"/>
+    </row>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.15">
+      <c r="C66" s="31"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="83"/>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="83"/>
+      <c r="J66" s="33"/>
+    </row>
+    <row r="67" spans="3:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C67" s="31"/>
+      <c r="D67" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="E67" s="149"/>
-      <c r="F67" s="149"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="63"/>
-      <c r="J67" s="37"/>
-    </row>
-    <row r="68" spans="3:10" s="9" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="35"/>
-      <c r="D68" s="168" t="s">
+      <c r="E67" s="121"/>
+      <c r="F67" s="121"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="33"/>
+    </row>
+    <row r="68" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="31"/>
+      <c r="D68" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="E68" s="168"/>
-      <c r="F68" s="168"/>
-      <c r="G68" s="64"/>
-      <c r="H68" s="64"/>
-      <c r="I68" s="64"/>
-      <c r="J68" s="37"/>
-    </row>
-    <row r="69" spans="3:10" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="C69" s="35"/>
-      <c r="D69" s="96" t="s">
+      <c r="E68" s="114"/>
+      <c r="F68" s="114"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
+      <c r="J68" s="33"/>
+    </row>
+    <row r="69" spans="3:10" ht="14" x14ac:dyDescent="0.15">
+      <c r="C69" s="31"/>
+      <c r="D69" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="E69" s="130" t="s">
+      <c r="E69" s="128" t="s">
         <v>25</v>
       </c>
-      <c r="F69" s="131"/>
-      <c r="G69" s="95"/>
-      <c r="H69" s="95"/>
-      <c r="I69" s="95"/>
-      <c r="J69" s="37"/>
-    </row>
-    <row r="70" spans="3:10" s="9" customFormat="1" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="35"/>
-      <c r="D70" s="97" t="s">
+      <c r="F69" s="129"/>
+      <c r="G69" s="83"/>
+      <c r="H69" s="83"/>
+      <c r="I69" s="83"/>
+      <c r="J69" s="33"/>
+    </row>
+    <row r="70" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="31"/>
+      <c r="D70" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="132"/>
-      <c r="F70" s="133"/>
-      <c r="G70" s="95"/>
-      <c r="H70" s="95"/>
-      <c r="I70" s="95"/>
-      <c r="J70" s="37"/>
-    </row>
-    <row r="71" spans="3:10" s="9" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="35"/>
-      <c r="D71" s="98" t="s">
+      <c r="E70" s="130"/>
+      <c r="F70" s="131"/>
+      <c r="G70" s="83"/>
+      <c r="H70" s="83"/>
+      <c r="I70" s="83"/>
+      <c r="J70" s="33"/>
+    </row>
+    <row r="71" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="31"/>
+      <c r="D71" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="E71" s="153"/>
-      <c r="F71" s="129"/>
-      <c r="G71" s="95"/>
-      <c r="H71" s="95"/>
-      <c r="I71" s="95"/>
-      <c r="J71" s="37"/>
-    </row>
-    <row r="72" spans="3:10" s="9" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="35"/>
-      <c r="D72" s="99" t="s">
+      <c r="E71" s="125"/>
+      <c r="F71" s="116"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="83"/>
+      <c r="I71" s="83"/>
+      <c r="J71" s="33"/>
+    </row>
+    <row r="72" spans="3:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C72" s="31"/>
+      <c r="D72" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="E72" s="128"/>
-      <c r="F72" s="129"/>
-      <c r="G72" s="95"/>
-      <c r="H72" s="95"/>
-      <c r="I72" s="95"/>
-      <c r="J72" s="37"/>
-    </row>
-    <row r="73" spans="3:10" s="9" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="35"/>
-      <c r="D73" s="99" t="s">
+      <c r="E72" s="115"/>
+      <c r="F72" s="116"/>
+      <c r="G72" s="83"/>
+      <c r="H72" s="83"/>
+      <c r="I72" s="83"/>
+      <c r="J72" s="33"/>
+    </row>
+    <row r="73" spans="3:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="31"/>
+      <c r="D73" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="146"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="37"/>
-    </row>
-    <row r="74" spans="3:10" s="9" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="35"/>
-      <c r="D74" s="99" t="s">
+      <c r="E73" s="117"/>
+      <c r="F73" s="118"/>
+      <c r="G73" s="83"/>
+      <c r="H73" s="83"/>
+      <c r="I73" s="83"/>
+      <c r="J73" s="33"/>
+    </row>
+    <row r="74" spans="3:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="31"/>
+      <c r="D74" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="128"/>
-      <c r="F74" s="129"/>
-      <c r="G74" s="95"/>
-      <c r="H74" s="95"/>
-      <c r="I74" s="95"/>
-      <c r="J74" s="37"/>
-    </row>
-    <row r="75" spans="3:10" s="9" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="35"/>
-      <c r="D75" s="99" t="s">
+      <c r="E74" s="115"/>
+      <c r="F74" s="116"/>
+      <c r="G74" s="83"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="33"/>
+    </row>
+    <row r="75" spans="3:10" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="31"/>
+      <c r="D75" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="E75" s="146"/>
-      <c r="F75" s="147"/>
-      <c r="G75" s="95"/>
-      <c r="H75" s="95"/>
-      <c r="I75" s="95"/>
-      <c r="J75" s="37"/>
-    </row>
-    <row r="76" spans="3:10" s="9" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="35"/>
-      <c r="D76" s="99" t="s">
+      <c r="E75" s="117"/>
+      <c r="F75" s="118"/>
+      <c r="G75" s="83"/>
+      <c r="H75" s="83"/>
+      <c r="I75" s="83"/>
+      <c r="J75" s="33"/>
+    </row>
+    <row r="76" spans="3:10" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="31"/>
+      <c r="D76" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="E76" s="128"/>
-      <c r="F76" s="129"/>
-      <c r="G76" s="95"/>
-      <c r="H76" s="95"/>
-      <c r="I76" s="95"/>
-      <c r="J76" s="37"/>
-    </row>
-    <row r="77" spans="3:10" s="9" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="35"/>
-      <c r="D77" s="99" t="s">
+      <c r="E76" s="115"/>
+      <c r="F76" s="116"/>
+      <c r="G76" s="83"/>
+      <c r="H76" s="83"/>
+      <c r="I76" s="83"/>
+      <c r="J76" s="33"/>
+    </row>
+    <row r="77" spans="3:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C77" s="31"/>
+      <c r="D77" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="E77" s="146"/>
-      <c r="F77" s="147"/>
-      <c r="G77" s="95"/>
-      <c r="H77" s="95"/>
-      <c r="I77" s="95"/>
-      <c r="J77" s="37"/>
-    </row>
-    <row r="78" spans="3:10" s="9" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="35"/>
-      <c r="D78" s="99" t="s">
+      <c r="E77" s="117"/>
+      <c r="F77" s="118"/>
+      <c r="G77" s="83"/>
+      <c r="H77" s="83"/>
+      <c r="I77" s="83"/>
+      <c r="J77" s="33"/>
+    </row>
+    <row r="78" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="31"/>
+      <c r="D78" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="E78" s="151"/>
-      <c r="F78" s="152"/>
-      <c r="G78" s="95"/>
-      <c r="H78" s="95"/>
-      <c r="I78" s="95"/>
-      <c r="J78" s="37"/>
-    </row>
-    <row r="79" spans="3:10" s="9" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="35"/>
-      <c r="D79" s="99" t="s">
+      <c r="E78" s="123"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="83"/>
+      <c r="H78" s="83"/>
+      <c r="I78" s="83"/>
+      <c r="J78" s="33"/>
+    </row>
+    <row r="79" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="31"/>
+      <c r="D79" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="E79" s="151"/>
-      <c r="F79" s="152"/>
-      <c r="G79" s="95"/>
-      <c r="H79" s="95"/>
-      <c r="I79" s="95"/>
-      <c r="J79" s="37"/>
-    </row>
-    <row r="80" spans="3:10" s="9" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="35"/>
-      <c r="D80" s="99" t="s">
+      <c r="E79" s="123"/>
+      <c r="F79" s="124"/>
+      <c r="G79" s="83"/>
+      <c r="H79" s="83"/>
+      <c r="I79" s="83"/>
+      <c r="J79" s="33"/>
+    </row>
+    <row r="80" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="31"/>
+      <c r="D80" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="E80" s="151"/>
-      <c r="F80" s="152"/>
-      <c r="G80" s="95"/>
-      <c r="H80" s="95"/>
-      <c r="I80" s="95"/>
-      <c r="J80" s="37"/>
-    </row>
-    <row r="81" spans="1:16" s="9" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="35"/>
-      <c r="D81" s="99" t="s">
+      <c r="E80" s="123"/>
+      <c r="F80" s="124"/>
+      <c r="G80" s="83"/>
+      <c r="H80" s="83"/>
+      <c r="I80" s="83"/>
+      <c r="J80" s="33"/>
+    </row>
+    <row r="81" spans="3:16" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C81" s="31"/>
+      <c r="D81" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="E81" s="151"/>
-      <c r="F81" s="152"/>
-      <c r="G81" s="95"/>
-      <c r="H81" s="95"/>
-      <c r="I81" s="95"/>
-      <c r="J81" s="37"/>
-    </row>
-    <row r="82" spans="1:16" s="9" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="35"/>
-      <c r="D82" s="99" t="s">
+      <c r="E81" s="123"/>
+      <c r="F81" s="124"/>
+      <c r="G81" s="83"/>
+      <c r="H81" s="83"/>
+      <c r="I81" s="83"/>
+      <c r="J81" s="33"/>
+    </row>
+    <row r="82" spans="3:16" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C82" s="31"/>
+      <c r="D82" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="E82" s="128"/>
-      <c r="F82" s="129"/>
-      <c r="G82" s="95"/>
-      <c r="H82" s="95"/>
-      <c r="I82" s="95"/>
-      <c r="J82" s="37"/>
-    </row>
-    <row r="83" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="35"/>
-      <c r="D83" s="95"/>
-      <c r="E83" s="95"/>
-      <c r="F83" s="95"/>
-      <c r="G83" s="95"/>
-      <c r="H83" s="95"/>
-      <c r="I83" s="95"/>
-      <c r="J83" s="37"/>
-    </row>
-    <row r="84" spans="1:16" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="35"/>
-      <c r="D84" s="42" t="s">
+      <c r="E82" s="115"/>
+      <c r="F82" s="116"/>
+      <c r="G82" s="83"/>
+      <c r="H82" s="83"/>
+      <c r="I82" s="83"/>
+      <c r="J82" s="33"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.15">
+      <c r="C83" s="31"/>
+      <c r="D83" s="83"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="83"/>
+      <c r="G83" s="83"/>
+      <c r="H83" s="83"/>
+      <c r="I83" s="83"/>
+      <c r="J83" s="33"/>
+    </row>
+    <row r="84" spans="3:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C84" s="31"/>
+      <c r="D84" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E84" s="95"/>
-      <c r="F84" s="95"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="95"/>
-      <c r="I84" s="95"/>
-      <c r="J84" s="37"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-    </row>
-    <row r="85" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="35"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="18"/>
-      <c r="J85" s="37"/>
-    </row>
-    <row r="86" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="156"/>
-      <c r="D86" s="157"/>
-      <c r="E86" s="157"/>
-      <c r="F86" s="157"/>
-      <c r="G86" s="157"/>
-      <c r="H86" s="157"/>
-      <c r="I86" s="157"/>
-      <c r="J86" s="158"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="1:16" ht="186" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="154" t="s">
+      <c r="E84" s="83"/>
+      <c r="F84" s="83"/>
+      <c r="G84" s="83"/>
+      <c r="H84" s="83"/>
+      <c r="I84" s="83"/>
+      <c r="J84" s="33"/>
+    </row>
+    <row r="85" spans="3:16" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C85" s="31"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="33"/>
+    </row>
+    <row r="86" spans="3:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="C86" s="91"/>
+      <c r="D86" s="92"/>
+      <c r="E86" s="92"/>
+      <c r="F86" s="92"/>
+      <c r="G86" s="92"/>
+      <c r="H86" s="92"/>
+      <c r="I86" s="92"/>
+      <c r="J86" s="93"/>
+    </row>
+    <row r="87" spans="3:16" ht="186" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C87" s="126" t="s">
         <v>100</v>
       </c>
-      <c r="D87" s="154"/>
-      <c r="E87" s="154"/>
-      <c r="F87" s="154"/>
-      <c r="G87" s="154"/>
-      <c r="H87" s="154"/>
-      <c r="I87" s="154"/>
-      <c r="J87" s="154"/>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="150"/>
-      <c r="D88" s="150"/>
-      <c r="E88" s="150"/>
-      <c r="F88" s="150"/>
-      <c r="G88" s="150"/>
-      <c r="H88" s="150"/>
-      <c r="I88" s="150"/>
-      <c r="J88" s="150"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
+      <c r="D87" s="126"/>
+      <c r="E87" s="126"/>
+      <c r="F87" s="126"/>
+      <c r="G87" s="126"/>
+      <c r="H87" s="126"/>
+      <c r="I87" s="126"/>
+      <c r="J87" s="126"/>
+    </row>
+    <row r="88" spans="3:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C88" s="122"/>
+      <c r="D88" s="122"/>
+      <c r="E88" s="122"/>
+      <c r="F88" s="122"/>
+      <c r="G88" s="122"/>
+      <c r="H88" s="122"/>
+      <c r="I88" s="122"/>
+      <c r="J88" s="122"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.15">
       <c r="C89" s="127"/>
       <c r="D89" s="127"/>
       <c r="E89" s="127"/>
@@ -6342,12 +5852,8 @@
       <c r="H89" s="127"/>
       <c r="I89" s="127"/>
       <c r="J89" s="127"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.15">
       <c r="C90" s="127"/>
       <c r="D90" s="127"/>
       <c r="E90" s="127"/>
@@ -6356,132 +5862,59 @@
       <c r="H90" s="127"/>
       <c r="I90" s="127"/>
       <c r="J90" s="127"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C92" s="12"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="31"/>
-      <c r="L93" s="31"/>
-      <c r="M93" s="31"/>
-      <c r="N93" s="31"/>
-      <c r="O93" s="31"/>
-      <c r="P93" s="31"/>
-    </row>
-    <row r="94" spans="1:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="30"/>
-      <c r="L94" s="30"/>
-      <c r="M94" s="30"/>
-      <c r="N94" s="30"/>
-      <c r="O94" s="30"/>
-      <c r="P94" s="30"/>
-    </row>
-    <row r="95" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="30"/>
-      <c r="L95" s="30"/>
-      <c r="M95" s="30"/>
-      <c r="N95" s="30"/>
-      <c r="O95" s="30"/>
-      <c r="P95" s="30"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-    </row>
-    <row r="103" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-    </row>
-    <row r="104" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
-    </row>
-    <row r="108" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.15">
+      <c r="C91" s="9"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.15">
+      <c r="C92" s="9"/>
+    </row>
+    <row r="93" spans="3:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K93" s="27"/>
+      <c r="L93" s="27"/>
+      <c r="M93" s="27"/>
+      <c r="N93" s="27"/>
+      <c r="O93" s="27"/>
+      <c r="P93" s="27"/>
+    </row>
+    <row r="94" spans="3:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K94" s="26"/>
+      <c r="L94" s="26"/>
+      <c r="M94" s="26"/>
+      <c r="N94" s="26"/>
+      <c r="O94" s="26"/>
+      <c r="P94" s="26"/>
+    </row>
+    <row r="95" spans="3:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K95" s="26"/>
+      <c r="L95" s="26"/>
+      <c r="M95" s="26"/>
+      <c r="N95" s="26"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="26"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="35">
+    <mergeCell ref="C89:J89"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E69:F70"/>
+    <mergeCell ref="K24:K43"/>
+    <mergeCell ref="C90:J90"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="D61:I64"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="C88:J88"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="C87:J87"/>
     <mergeCell ref="C4:J5"/>
     <mergeCell ref="C86:J86"/>
     <mergeCell ref="D54:I54"/>
@@ -6498,25 +5931,6 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="C88:J88"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="C87:J87"/>
-    <mergeCell ref="C89:J89"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="E69:F70"/>
-    <mergeCell ref="K24:K43"/>
-    <mergeCell ref="C90:J90"/>
-    <mergeCell ref="D60:I60"/>
-    <mergeCell ref="D61:I64"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
@@ -6537,64 +5951,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B12:K18"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="C14:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="70"/>
-      <c r="C14" s="71"/>
-      <c r="G14" s="73" t="s">
+    <row r="14" spans="3:11" x14ac:dyDescent="0.15">
+      <c r="C14" s="38"/>
+      <c r="G14" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K14" s="38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="70"/>
-      <c r="C15" s="71"/>
-      <c r="G15" s="44" t="s">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.15">
+      <c r="C15" s="38"/>
+      <c r="G15" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="K15" s="44" t="s">
+      <c r="K15" s="38" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="70"/>
-      <c r="C16" s="71"/>
-      <c r="G16" s="44" t="s">
+    <row r="16" spans="3:11" x14ac:dyDescent="0.15">
+      <c r="C16" s="38"/>
+      <c r="G16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="K16" s="44" t="s">
+      <c r="I16" s="38"/>
+      <c r="K16" s="38" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="K17" s="44" t="s">
+    <row r="17" spans="11:11" x14ac:dyDescent="0.15">
+      <c r="K17" s="38" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
